--- a/groups.xlsx
+++ b/groups.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="5928"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="5928" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -22,9 +22,10 @@
     <sheet name="Лист8" sheetId="8" r:id="rId8"/>
     <sheet name="Лист9" sheetId="9" r:id="rId9"/>
     <sheet name="Лист11" sheetId="11" r:id="rId10"/>
+    <sheet name="Лист10" sheetId="12" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Лист9!$B$1:$C$403</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Лист9!$B$1:$C$153</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2826" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2840" uniqueCount="560">
   <si>
     <t>ADC</t>
   </si>
@@ -1713,6 +1714,9 @@
   </si>
   <si>
     <t>&lt;operat1&gt; op_source_1</t>
+  </si>
+  <si>
+    <t>ГАРАНТИРОВАННО УНИКАЛЬНЫЕ</t>
   </si>
 </sst>
 </file>
@@ -1758,7 +1762,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1767,6 +1771,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -7733,10 +7740,10 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AZ29"/>
+  <dimension ref="A1:AZ100"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>277</v>
       </c>
@@ -7755,17 +7762,8 @@
       <c r="G1" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="V1" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="W1" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="X1" s="2">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>277</v>
       </c>
@@ -7784,17 +7782,8 @@
       <c r="G2" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="V2" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="X2" s="2">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>282</v>
       </c>
@@ -7831,8 +7820,26 @@
       <c r="O4" s="2">
         <v>386</v>
       </c>
-    </row>
-    <row r="5" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="Q4" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="W4" s="2">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>282</v>
       </c>
@@ -7869,8 +7876,26 @@
       <c r="O5" s="2">
         <v>386</v>
       </c>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Q5" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="W5" s="2">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>376</v>
       </c>
@@ -7917,7 +7942,7 @@
         <v>8086</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>376</v>
       </c>
@@ -7964,7 +7989,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>376</v>
       </c>
@@ -8011,7 +8036,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
         <v>324</v>
       </c>
@@ -8031,7 +8056,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
         <v>324</v>
       </c>
@@ -8051,7 +8076,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
         <v>347</v>
       </c>
@@ -8070,8 +8095,9 @@
       <c r="H14" s="2" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
         <v>347</v>
       </c>
@@ -8091,7 +8117,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B16" s="2" t="s">
         <v>347</v>
       </c>
@@ -8132,380 +8158,2908 @@
       </c>
     </row>
     <row r="19" spans="1:52" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>335</v>
+      </c>
       <c r="B19" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="U19" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="V19" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="W19" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="Y19" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="Z19" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="AA19" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="AC19" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="AD19" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="AE19" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="AG19" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="AH19" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="AI19" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="AK19" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="AL19" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="AM19" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="AO19" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="AP19" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="AQ19" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="AS19" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="AT19" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="AU19" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="AW19" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="AX19" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="AY19" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="20" spans="1:52" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
         <v>335</v>
       </c>
+      <c r="B20" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="U20" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="V20" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="W20" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="Y20" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="Z20" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="AA20" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="AC20" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="AD20" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="AE20" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="AG20" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="AH20" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="AI20" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="AK20" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="AL20" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="AM20" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="AO20" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="AP20" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="AQ20" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="AS20" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="AT20" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="AU20" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="AW20" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="AX20" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="AY20" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="21" spans="1:52" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="U21" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="V21" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="W21" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="Y21" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="Z21" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="AA21" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="AC21" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="AD21" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="AE21" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="AG21" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="AH21" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="AI21" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="AK21" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="AL21" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="AM21" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="AO21" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="AP21" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="AQ21" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="AS21" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="AT21" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="AU21" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="AW21" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="AX21" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="AY21" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="22" spans="1:52" x14ac:dyDescent="0.3">
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="2"/>
+      <c r="T22" s="2"/>
+      <c r="V22" s="2"/>
+      <c r="W22" s="2"/>
+      <c r="X22" s="2"/>
+      <c r="Z22" s="2"/>
+      <c r="AA22" s="2"/>
+      <c r="AB22" s="2"/>
+      <c r="AD22" s="2"/>
+      <c r="AE22" s="2"/>
+      <c r="AF22" s="2"/>
+      <c r="AH22" s="2"/>
+      <c r="AI22" s="2"/>
+      <c r="AJ22" s="2"/>
+      <c r="AL22" s="2"/>
+      <c r="AM22" s="2"/>
+      <c r="AN22" s="2"/>
+      <c r="AP22" s="2"/>
+      <c r="AQ22" s="2"/>
+      <c r="AR22" s="2"/>
+      <c r="AT22" s="2"/>
+      <c r="AU22" s="2"/>
+      <c r="AV22" s="2"/>
+      <c r="AX22" s="2"/>
+      <c r="AY22" s="2"/>
+      <c r="AZ22" s="2"/>
+    </row>
+    <row r="23" spans="1:52" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="U23" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="V23" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="W23" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="Y23" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="Z23" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="AA23" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="AC23" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="AD23" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="AE23" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="24" spans="1:52" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="S24" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="U24" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="V24" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="W24" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="Y24" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="Z24" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="AA24" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="AC24" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="AD24" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="AE24" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="25" spans="1:52" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q25" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="U25" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="V25" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="W25" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="Y25" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="Z25" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="AA25" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="AC25" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="AD25" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="AE25" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="28" spans="1:52" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>555</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q28" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="S28" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="T28" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="U28" s="2" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="29" spans="1:52" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>557</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="O29" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="P29" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q29" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="S29" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="T29" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="U29" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="30" spans="1:52" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G30" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q30" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="S30" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="T30" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="U30" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="31" spans="1:52" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>556</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="I31" s="2">
+        <v>286</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q31" s="2">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="32" spans="1:52" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C34" s="2">
+        <v>286</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="G34" s="2">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C35" s="2">
+        <v>286</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="G35" s="2">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C36" s="2">
+        <v>286</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G36" s="2">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C37" s="2">
+        <v>386</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G37" s="2">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C39" s="2">
+        <v>8086</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="G39" s="2">
+        <v>8086</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="C40" s="2">
+        <v>8086</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="G40" s="2">
+        <v>8086</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="C41" s="2">
+        <v>386</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="G41" s="2">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C42" s="2">
+        <v>8086</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="G42" s="2">
+        <v>8086</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="C43" s="2">
+        <v>8086</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="G43" s="2">
+        <v>8086</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="C44" s="2">
+        <v>386</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="G44" s="2">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="G46" s="2">
+        <v>8086</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="M46" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="N46" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="O46" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="Q46" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="R46" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="S46" s="2" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="M47" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="N47" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="O47" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="Q47" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="R47" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="S47" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="C49" s="2">
+        <v>386</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="G49" s="2">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="C50" s="2">
+        <v>386</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="G50" s="2">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="C51" s="2">
+        <v>386</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="G51" s="2">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C52" s="2">
+        <v>386</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="G52" s="2">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="C53" s="2">
+        <v>386</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="G53" s="2">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="C54" s="2">
+        <v>386</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="G54" s="2">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="C55" s="2">
+        <v>386</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="G55" s="2">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="C56" s="2">
+        <v>386</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="G56" s="2">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="M58" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="N58" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="O58" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="K59" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="M59" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="N59" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="O59" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A60" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="M60" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="N60" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="O60" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A61" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="M61" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="N61" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="O61" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A62" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="M62" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="N62" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="O62" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A63" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="K63" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="M63" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="N63" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="O63" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="65" spans="1:27" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A65" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="K65" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="M65" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="N65" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="O65" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q65" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="R65" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="S65" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="U65" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="V65" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="W65" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="Y65" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="Z65" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="AA65" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="66" spans="1:27" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A66" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="M66" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="N66" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="O66" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q66" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="R66" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="S66" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="U66" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="V66" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="W66" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="Y66" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="Z66" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="AA66" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="68" spans="1:27" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="M68" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="N68" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="O68" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q68" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="R68" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="S68" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="69" spans="1:27" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="M69" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="N69" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="O69" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q69" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="R69" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="S69" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="71" spans="1:27" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A71" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="72" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A72" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="74" spans="1:27" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A74" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="I74" s="2"/>
+      <c r="J74" s="2"/>
+      <c r="K74" s="2"/>
+    </row>
+    <row r="75" spans="1:27" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A75" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="I75" s="2"/>
+      <c r="J75" s="2"/>
+      <c r="K75" s="2"/>
+    </row>
+    <row r="76" spans="1:27" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="I76" s="2"/>
+      <c r="J76" s="2"/>
+      <c r="K76" s="2"/>
+    </row>
+    <row r="77" spans="1:27" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="I77" s="2"/>
+      <c r="J77" s="2"/>
+      <c r="K77" s="2"/>
+    </row>
+    <row r="78" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="I78" s="2"/>
+      <c r="J78" s="2"/>
+      <c r="K78" s="2"/>
+    </row>
+    <row r="79" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="I79" s="2"/>
+      <c r="J79" s="2"/>
+      <c r="K79" s="2"/>
+    </row>
+    <row r="80" spans="1:27" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A80" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="M80" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="N80" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="O80" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A81" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="K81" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="M81" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="N81" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="O81" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A82" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="K82" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="M82" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="N82" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="O82" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A83" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="J83" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="K83" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="M83" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="N83" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="O83" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A84" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="K84" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="M84" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="N84" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="O84" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A85" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="J85" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="K85" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="M85" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="N85" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="O85" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A87" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="J87" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="K87" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A88" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="C88" s="2">
+        <v>186</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="G88" s="2">
+        <v>186</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="J88" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="K88" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A89" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="C89" s="2">
+        <v>186</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="G89" s="2">
+        <v>186</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="J89" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="K89" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A91" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C91" s="2">
+        <v>386</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="G91" s="2">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A92" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="C92" s="2">
+        <v>386</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="G92" s="2">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A93" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C93" s="2">
+        <v>386</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="G93" s="2">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A94" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="C94" s="2">
+        <v>386</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="G94" s="2">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C97" s="2">
+        <v>8086</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C98" s="2">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A99" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A100" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="7" max="7" width="12.5546875" customWidth="1"/>
+    <col min="8" max="8" width="18.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" s="2">
+        <v>8086</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="N1" s="2">
+        <v>8086</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H2" s="2">
+        <v>8086</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="N2" s="2">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H3" s="2">
+        <v>386</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="H4" s="2">
+        <v>386</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="N4" s="2">
+        <v>8086</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="H5" s="2">
+        <v>386</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="H6" s="2">
+        <v>386</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="N6" s="2">
+        <v>8086</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="H7" s="2">
+        <v>386</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="H8" s="2">
+        <v>186</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="N8" s="2">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+    </row>
+    <row r="10" spans="1:14" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="H10" s="2">
+        <v>186</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="M11" s="2">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="H12" s="2">
+        <v>186</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="M12" s="2">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="H14" s="2">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C16" s="2">
+        <v>8086</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="H16" s="2">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C17" s="2">
+        <v>386</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="H18" s="2">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>311</v>
+      </c>
       <c r="C19" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>328</v>
+        <v>312</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>334</v>
+        <v>366</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>322</v>
+        <v>432</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="P19" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="R19" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="S19" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="T19" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="V19" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="W19" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="X19" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="Z19" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="AA19" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="AB19" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="AD19" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="AE19" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="AF19" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="AH19" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="AI19" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="AJ19" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="AL19" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="AM19" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="AN19" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="AP19" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="AQ19" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="AR19" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="AT19" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="AU19" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="AV19" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="AX19" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="AY19" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="AZ19" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="20" spans="1:52" ht="28.8" x14ac:dyDescent="0.3">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>287</v>
+      </c>
       <c r="B20" s="2" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>334</v>
+        <v>366</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="N20" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="O20" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="P20" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="R20" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="S20" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="T20" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="V20" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="W20" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="X20" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="Z20" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="AA20" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="AB20" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="AD20" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="AE20" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="AF20" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="AH20" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="AI20" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="AJ20" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="AL20" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="AM20" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="AN20" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="AP20" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="AQ20" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="AR20" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="AT20" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="AU20" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="AV20" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="AX20" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="AY20" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="AZ20" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="21" spans="1:52" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B21" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>393</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="H20" s="2">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="172.8" x14ac:dyDescent="0.3">
       <c r="F21" s="2" t="s">
-        <v>334</v>
+        <v>366</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>388</v>
+        <v>434</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="P21" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="R21" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="S21" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="T21" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="V21" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="W21" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="X21" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="Z21" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="AA21" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="AB21" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="AD21" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="AE21" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="AF21" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="AH21" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="AI21" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="AJ21" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="AL21" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="AM21" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="AN21" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="AP21" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="AQ21" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="AR21" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="AT21" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="AU21" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="AV21" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="AX21" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="AY21" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="AZ21" s="2" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="25" spans="1:52" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="26" spans="1:52" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="28" spans="1:52" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="29" spans="1:52" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>558</v>
+        <v>430</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="F22" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="H22" s="2">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="F23" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="F24" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="H24" s="2">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="F25" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="F26" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="H26" s="2">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="F27" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="F28" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="H28" s="2">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="F29" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="F30" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="H30" s="2">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="F31" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>430</v>
       </c>
     </row>
   </sheetData>
@@ -8573,7 +11127,7 @@
         <v>62</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D2:D7" si="0">IF(B3=F3,1)</f>
+        <f t="shared" ref="D3:D7" si="0">IF(B3=F3,1)</f>
         <v>1</v>
       </c>
       <c r="E3" s="2" t="s">
@@ -9300,7 +11854,7 @@
         <v>8086</v>
       </c>
       <c r="G3">
-        <f t="shared" ref="G3:G40" si="0">IF(B3=E3,1,0)</f>
+        <f t="shared" ref="G3:G13" si="0">IF(B3=E3,1,0)</f>
         <v>1</v>
       </c>
       <c r="H3" s="2" t="s">
@@ -9313,7 +11867,7 @@
         <v>8086</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K40" si="1">IF(B3=I3,1,0)</f>
+        <f t="shared" ref="K3:K13" si="1">IF(B3=I3,1,0)</f>
         <v>1</v>
       </c>
       <c r="L3" s="2" t="s">
@@ -9326,7 +11880,7 @@
         <v>22</v>
       </c>
       <c r="O3">
-        <f t="shared" ref="O3:O40" si="2">IF(B3=M3,1,0)</f>
+        <f t="shared" ref="O3:O13" si="2">IF(B3=M3,1,0)</f>
         <v>1</v>
       </c>
       <c r="P3" s="2" t="s">
@@ -9339,7 +11893,7 @@
         <v>8086</v>
       </c>
       <c r="S3">
-        <f t="shared" ref="S3:S40" si="3">IF(B3=Q3,1,0)</f>
+        <f t="shared" ref="S3:S13" si="3">IF(B3=Q3,1,0)</f>
         <v>1</v>
       </c>
       <c r="T3" s="2" t="s">
@@ -9352,7 +11906,7 @@
         <v>8086</v>
       </c>
       <c r="W3">
-        <f t="shared" ref="W3:W40" si="4">IF(B3=U3,1,0)</f>
+        <f t="shared" ref="W3:W13" si="4">IF(B3=U3,1,0)</f>
         <v>1</v>
       </c>
       <c r="X3" s="2" t="s">
@@ -9365,7 +11919,7 @@
         <v>8086</v>
       </c>
       <c r="AA3">
-        <f t="shared" ref="AA3:AA40" si="5">IF(B3=Y3,1,0)</f>
+        <f t="shared" ref="AA3:AA13" si="5">IF(B3=Y3,1,0)</f>
         <v>1</v>
       </c>
       <c r="AB3" s="2" t="s">
@@ -9378,7 +11932,7 @@
         <v>8086</v>
       </c>
       <c r="AE3">
-        <f t="shared" ref="AE3:AE40" si="6">IF(B3=AC3,1,0)</f>
+        <f t="shared" ref="AE3:AE13" si="6">IF(B3=AC3,1,0)</f>
         <v>1</v>
       </c>
     </row>
@@ -10538,7 +13092,7 @@
       <c r="AC18" s="2"/>
       <c r="AD18" s="2"/>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:30" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>108</v>
       </c>
@@ -10566,7 +13120,7 @@
       <c r="AC19" s="2"/>
       <c r="AD19" s="2"/>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:30" ht="72" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>109</v>
       </c>
@@ -10594,7 +13148,7 @@
       <c r="AC20" s="2"/>
       <c r="AD20" s="2"/>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:30" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>110</v>
       </c>
@@ -10622,7 +13176,7 @@
       <c r="AC21" s="2"/>
       <c r="AD21" s="2"/>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:30" ht="72" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>111</v>
       </c>
@@ -10650,7 +13204,7 @@
       <c r="AC22" s="2"/>
       <c r="AD22" s="2"/>
     </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:30" ht="72" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>112</v>
       </c>
@@ -10678,7 +13232,7 @@
       <c r="AC23" s="2"/>
       <c r="AD23" s="2"/>
     </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:30" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>113</v>
       </c>
@@ -11535,7 +14089,7 @@
         <v>386</v>
       </c>
       <c r="G3">
-        <f t="shared" ref="G3:G40" si="0">IF(B3=E3,1,0)</f>
+        <f t="shared" ref="G3:G10" si="0">IF(B3=E3,1,0)</f>
         <v>1</v>
       </c>
       <c r="H3" s="2" t="s">
@@ -11548,7 +14102,7 @@
         <v>386</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K40" si="1">IF(B3=I3,1,0)</f>
+        <f t="shared" ref="K3:K10" si="1">IF(B3=I3,1,0)</f>
         <v>1</v>
       </c>
       <c r="L3" s="2" t="s">
@@ -11561,7 +14115,7 @@
         <v>386</v>
       </c>
       <c r="O3">
-        <f t="shared" ref="O3:O40" si="2">IF(B3=M3,1,0)</f>
+        <f t="shared" ref="O3:O10" si="2">IF(B3=M3,1,0)</f>
         <v>1</v>
       </c>
       <c r="P3" s="2"/>
@@ -13009,7 +15563,7 @@
         <v>126</v>
       </c>
       <c r="G3">
-        <f t="shared" ref="G3:G40" si="0">IF(B3=E3,1,0)</f>
+        <f t="shared" ref="G3:G9" si="0">IF(B3=E3,1,0)</f>
         <v>1</v>
       </c>
       <c r="H3" s="2" t="s">
@@ -13022,7 +15576,7 @@
         <v>486</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K40" si="1">IF(B3=I3,1,0)</f>
+        <f t="shared" ref="K3:K9" si="1">IF(B3=I3,1,0)</f>
         <v>1</v>
       </c>
       <c r="L3" s="2"/>
@@ -14923,10 +17477,11 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C352"/>
+  <dimension ref="A1:C102"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="31.6640625" customWidth="1"/>
+    <col min="2" max="2" width="12.21875" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
@@ -14942,3867 +17497,1106 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>287</v>
+        <v>318</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C2" s="2">
+        <v>8086</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>287</v>
+        <v>318</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>290</v>
+        <v>302</v>
+      </c>
+      <c r="C3" s="2">
+        <v>8086</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>287</v>
+        <v>344</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>291</v>
+        <v>322</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>292</v>
+        <v>321</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>287</v>
+        <v>344</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>265</v>
+        <v>388</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>287</v>
+        <v>357</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>294</v>
+        <v>320</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>287</v>
+        <v>357</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>296</v>
+        <v>322</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>292</v>
+        <v>321</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>287</v>
+        <v>357</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>269</v>
+        <v>388</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>297</v>
+        <v>392</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>287</v>
+        <v>451</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>298</v>
+        <v>452</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>287</v>
+        <v>373</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>301</v>
+        <v>455</v>
+      </c>
+      <c r="C10" s="2">
+        <v>8086</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>287</v>
+        <v>373</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C21" s="2" t="s">
         <v>254</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="C17" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="C18" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>318</v>
+        <v>373</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="C22" s="2">
-        <v>8086</v>
+        <v>303</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>318</v>
+        <v>373</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="C23" s="2">
-        <v>8086</v>
+        <v>304</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>319</v>
+        <v>373</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>321</v>
+        <v>250</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>319</v>
+        <v>373</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>389</v>
+        <v>306</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>321</v>
+        <v>250</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>319</v>
+        <v>373</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>319</v>
+        <v>373</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+        <v>308</v>
+      </c>
+      <c r="C27" s="2">
+        <v>8086</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>319</v>
+        <v>373</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>321</v>
+        <v>309</v>
+      </c>
+      <c r="C28" s="2">
+        <v>386</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>319</v>
+        <v>373</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>388</v>
+        <v>310</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>336</v>
+        <v>373</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>336</v>
+        <v>373</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>336</v>
+        <v>373</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>391</v>
+        <v>315</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>321</v>
+        <v>288</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>336</v>
+        <v>373</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>388</v>
+        <v>64</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>392</v>
+        <v>293</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>339</v>
+        <v>373</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>320</v>
+        <v>65</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>321</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>339</v>
+        <v>374</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>322</v>
+        <v>283</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>339</v>
+        <v>374</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>391</v>
+        <v>285</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>321</v>
+        <v>465</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>339</v>
+        <v>374</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>388</v>
+        <v>440</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>392</v>
+        <v>466</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>340</v>
+        <v>374</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>320</v>
+        <v>444</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>321</v>
+        <v>467</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>340</v>
+        <v>473</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>321</v>
+        <v>375</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>340</v>
+        <v>473</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>322</v>
+        <v>59</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>321</v>
+        <v>375</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>340</v>
+        <v>378</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>340</v>
+        <v>378</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>391</v>
+        <v>482</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>340</v>
+        <v>377</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>388</v>
+        <v>484</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>342</v>
+        <v>377</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+        <v>486</v>
+      </c>
+      <c r="C44" s="2">
+        <v>8086</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>342</v>
+        <v>377</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>321</v>
+        <v>487</v>
+      </c>
+      <c r="C45" s="2">
+        <v>386</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>342</v>
+        <v>377</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>390</v>
+        <v>488</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>342</v>
+        <v>377</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>322</v>
+        <v>489</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>321</v>
+        <v>490</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>342</v>
+        <v>377</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>391</v>
+        <v>491</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>342</v>
+        <v>377</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+        <v>493</v>
+      </c>
+      <c r="C49" s="2">
+        <v>8086</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>344</v>
+        <v>377</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+        <v>494</v>
+      </c>
+      <c r="C50" s="2">
+        <v>8086</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>344</v>
+        <v>377</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+        <v>495</v>
+      </c>
+      <c r="C51" s="2">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>394</v>
+        <v>377</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>320</v>
+        <v>496</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>394</v>
+        <v>377</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>395</v>
+        <v>498</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>396</v>
+        <v>377</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>320</v>
+        <v>499</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>396</v>
+        <v>377</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>395</v>
+        <v>501</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>397</v>
+        <v>377</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>320</v>
+        <v>503</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>397</v>
+        <v>377</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>395</v>
+        <v>504</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>398</v>
+        <v>377</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>320</v>
+        <v>505</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>398</v>
+        <v>377</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>395</v>
+        <v>506</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>399</v>
+        <v>377</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>320</v>
+        <v>508</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>321</v>
+        <v>507</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>399</v>
+        <v>377</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>321</v>
+        <v>509</v>
+      </c>
+      <c r="C61" s="2">
+        <v>8086</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>345</v>
+        <v>377</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>321</v>
+        <v>510</v>
+      </c>
+      <c r="C62" s="2">
+        <v>8086</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>345</v>
+        <v>377</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>321</v>
+        <v>280</v>
+      </c>
+      <c r="C63" s="2">
+        <v>8086</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>321</v>
+        <v>281</v>
+      </c>
+      <c r="C64" s="2">
+        <v>8086</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>321</v>
+        <v>417</v>
+      </c>
+      <c r="C65" s="2">
+        <v>386</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>346</v>
+        <v>377</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>321</v>
+        <v>418</v>
+      </c>
+      <c r="C66" s="2">
+        <v>386</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>346</v>
+        <v>377</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>321</v>
+        <v>511</v>
+      </c>
+      <c r="C67" s="2">
+        <v>8086</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>401</v>
+        <v>377</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>321</v>
+        <v>283</v>
+      </c>
+      <c r="C68" s="2">
+        <v>8086</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>401</v>
+        <v>377</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>321</v>
+        <v>285</v>
+      </c>
+      <c r="C69" s="2">
+        <v>386</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>402</v>
+        <v>377</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>403</v>
+        <v>512</v>
+      </c>
+      <c r="C70" s="2">
+        <v>8086</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>402</v>
+        <v>377</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>403</v>
+        <v>440</v>
+      </c>
+      <c r="C71" s="2">
+        <v>8086</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>404</v>
+        <v>377</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>321</v>
+        <v>444</v>
+      </c>
+      <c r="C72" s="2">
+        <v>386</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>404</v>
+        <v>377</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>321</v>
+        <v>513</v>
+      </c>
+      <c r="C73" s="2">
+        <v>8086</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>405</v>
+        <v>377</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>321</v>
+        <v>514</v>
+      </c>
+      <c r="C74" s="2">
+        <v>8086</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>405</v>
+        <v>377</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>321</v>
+        <v>515</v>
+      </c>
+      <c r="C75" s="2">
+        <v>386</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>348</v>
+        <v>377</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>406</v>
+        <v>516</v>
+      </c>
+      <c r="C76" s="2">
+        <v>8086</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>407</v>
+        <v>377</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>321</v>
+        <v>517</v>
+      </c>
+      <c r="C77" s="2">
+        <v>8086</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>349</v>
+        <v>377</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>321</v>
+        <v>518</v>
+      </c>
+      <c r="C78" s="2">
+        <v>386</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>349</v>
+        <v>379</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>321</v>
+        <v>481</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>349</v>
+        <v>379</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>390</v>
+        <v>454</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>321</v>
+        <v>524</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>349</v>
+        <v>55</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+        <v>509</v>
+      </c>
+      <c r="C81" s="2">
+        <v>8086</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>349</v>
+        <v>55</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>321</v>
+        <v>510</v>
+      </c>
+      <c r="C82" s="2">
+        <v>8086</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>349</v>
+        <v>55</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>392</v>
+        <v>280</v>
+      </c>
+      <c r="C83" s="2">
+        <v>8086</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>350</v>
+        <v>55</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+        <v>281</v>
+      </c>
+      <c r="C84" s="2">
+        <v>8086</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>350</v>
+        <v>55</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>321</v>
+        <v>417</v>
+      </c>
+      <c r="C85" s="2">
+        <v>386</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>350</v>
+        <v>55</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>392</v>
+        <v>418</v>
+      </c>
+      <c r="C86" s="2">
+        <v>386</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>351</v>
+        <v>55</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>321</v>
+        <v>445</v>
+      </c>
+      <c r="C87" s="2">
+        <v>8086</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
-        <v>352</v>
+        <v>55</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>406</v>
+        <v>446</v>
+      </c>
+      <c r="C88" s="2">
+        <v>8086</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>408</v>
+        <v>55</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>321</v>
+        <v>447</v>
+      </c>
+      <c r="C89" s="2">
+        <v>386</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
-        <v>353</v>
+        <v>55</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>406</v>
+        <v>513</v>
+      </c>
+      <c r="C90" s="2">
+        <v>8086</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
-        <v>353</v>
+        <v>55</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>354</v>
+        <v>514</v>
+      </c>
+      <c r="C91" s="2">
+        <v>8086</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
-        <v>355</v>
+        <v>55</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>321</v>
+        <v>515</v>
+      </c>
+      <c r="C92" s="2">
+        <v>386</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
-        <v>356</v>
+        <v>55</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>321</v>
+        <v>516</v>
+      </c>
+      <c r="C93" s="2">
+        <v>8086</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
-        <v>357</v>
+        <v>55</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>321</v>
+        <v>517</v>
+      </c>
+      <c r="C94" s="2">
+        <v>8086</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
-        <v>357</v>
+        <v>55</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>321</v>
+        <v>518</v>
+      </c>
+      <c r="C95" s="2">
+        <v>386</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
-        <v>357</v>
+        <v>385</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>388</v>
+        <v>283</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
-        <v>410</v>
+        <v>385</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>315</v>
+        <v>281</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>406</v>
+        <v>386</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>411</v>
+        <v>385</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>315</v>
+        <v>285</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
-        <v>412</v>
+        <v>385</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>315</v>
+        <v>418</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A100" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>354</v>
+        <v>386</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
-        <v>359</v>
+        <v>387</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>321</v>
+        <v>315</v>
+      </c>
+      <c r="C101" s="2">
+        <v>386</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>359</v>
+        <v>387</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A103" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A104" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A105" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A106" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A107" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A108" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A109" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="B109" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A110" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="B110" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A111" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="B111" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A112" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="B112" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A113" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A114" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="B114" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A115" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A116" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="B116" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A117" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A118" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="B118" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A119" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="B119" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="C119" s="2" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A120" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="B120" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A121" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A122" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="B122" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A123" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="B123" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A124" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="B124" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A125" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="B125" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="C125" s="2" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A126" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A127" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="B127" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C127" s="2" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A128" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="B128" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A129" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="B129" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="C129" s="2" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A130" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="B130" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A131" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="B131" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="C131" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A132" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="B132" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A133" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="B133" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A134" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A135" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="B135" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C135" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A136" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="B136" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C136" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A137" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="B137" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C137" s="2">
+        <v>553</v>
+      </c>
+      <c r="C102" s="2">
         <v>386</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A138" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="B138" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C138" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A139" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="B139" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="C139" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A140" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C140" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A141" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="B141" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="C141" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A142" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="B142" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="C142" s="2">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A143" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="B143" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="C143" s="2" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A144" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="B144" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="C144" s="2">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A145" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="B145" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="C145" s="2" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A146" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="B146" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="C146" s="2">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A147" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="B147" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A148" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="B148" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="C148" s="2">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A149" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="B149" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="C149" s="2" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A150" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="B150" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="C150" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A151" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="B151" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="C151" s="2" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A152" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="B152" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="C152" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A153" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="B153" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A154" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="B154" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="C154" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A155" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="B155" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="C155" s="2" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A156" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="B156" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="C156" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A157" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="B157" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="C157" s="2" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A158" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="B158" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="C158" s="2">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A159" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="B159" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="C159" s="2" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A160" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="B160" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="C160" s="2">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A161" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="B161" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="C161" s="2" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A162" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="B162" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="C162" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A163" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="B163" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="C163" s="2" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A164" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="B164" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="C164" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A165" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="B165" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="C165" s="2" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A166" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="B166" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="C166" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A167" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="B167" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="C167" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A168" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="B168" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="C168" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A169" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="B169" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="C169" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A170" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="B170" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="C170" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A171" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="B171" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="C171" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A172" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="B172" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="C172" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A173" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="B173" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="C173" s="2" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A174" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="B174" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="C174" s="2" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A175" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="B175" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="C175" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A176" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="B176" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="C176" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A177" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="B177" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="C177" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A178" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="B178" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="C178" s="2" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A179" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="B179" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="C179" s="2" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A180" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="B180" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="C180" s="2" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A181" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="B181" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="C181" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A182" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="B182" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="C182" s="2" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A183" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="B183" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="C183" s="2" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A184" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="B184" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="C184" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A185" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="B185" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="C185" s="2" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A186" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="B186" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C186" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A187" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="B187" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="C187" s="2" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A188" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="B188" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="C188" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A189" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="B189" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="C189" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A190" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="B190" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="C190" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A191" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="B191" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="C191" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A192" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="B192" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="C192" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A193" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="B193" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="C193" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A194" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="B194" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="C194" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A195" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="B195" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="C195" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A196" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="B196" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="C196" s="2" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="197" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A197" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="B197" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="C197" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A198" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="B198" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="C198" s="2" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A199" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="B199" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="C199" s="2" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A200" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="B200" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C200" s="2" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A201" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="B201" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C201" s="2" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A202" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="B202" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C202" s="2" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A203" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="B203" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C203" s="2" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A204" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="B204" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="C204" s="2" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A205" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="B205" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="C205" s="2" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A206" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="B206" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C206" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A207" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="B207" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C207" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A208" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="B208" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C208" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A209" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="B209" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C209" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A210" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="B210" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="C210" s="2" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A211" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="B211" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="C211" s="2" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A212" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="B212" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="C212" s="2" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A213" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="B213" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="C213" s="2" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A214" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="B214" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C214" s="2" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="215" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A215" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="B215" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C215" s="2" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="216" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A216" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="B216" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="C216" s="2" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="217" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A217" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B217" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="C217" s="2" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="218" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A218" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B218" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="C218" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="219" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A219" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B219" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="C219" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="220" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A220" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B220" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="C220" s="2" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="221" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A221" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B221" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="C221" s="2" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A222" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B222" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="C222" s="2" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="223" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A223" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B223" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C223" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A224" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B224" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="C224" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A225" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B225" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="C225" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A226" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B226" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="C226" s="2" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A227" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B227" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="C227" s="2" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A228" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B228" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="C228" s="2" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="229" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A229" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B229" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="C229" s="2" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="230" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A230" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B230" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="C230" s="2" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A231" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B231" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="C231" s="2" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="232" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A232" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B232" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="C232" s="2" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A233" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B233" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="C233" s="2" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="234" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A234" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B234" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="C234" s="2" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="235" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A235" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B235" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="C235" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="236" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A236" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B236" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="C236" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="237" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A237" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B237" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="C237" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A238" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B238" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="C238" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A239" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B239" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="C239" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A240" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B240" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="C240" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="241" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A241" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B241" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="C241" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="242" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A242" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B242" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C242" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="243" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A243" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B243" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C243" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="244" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A244" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B244" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="C244" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A245" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B245" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="C245" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A246" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B246" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="C246" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A247" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B247" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="C247" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="248" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A248" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B248" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="C248" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="249" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A249" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B249" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="C249" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="250" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A250" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B250" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="C250" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="251" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A251" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B251" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="C251" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="252" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A252" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B252" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="C252" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="253" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A253" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="B253" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C253" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="254" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A254" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="B254" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="C254" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="255" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A255" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="B255" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="C255" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="256" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A256" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="B256" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="C256" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="257" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A257" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="B257" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C257" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="258" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A258" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="B258" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="C258" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="259" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A259" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="B259" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="C259" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="260" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A260" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="B260" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="C260" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A261" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="B261" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C261" s="2" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="262" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A262" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="B262" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="C262" s="2" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="263" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A263" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="B263" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="C263" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="264" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A264" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="B264" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="C264" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="265" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A265" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="B265" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="C265" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="266" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A266" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="B266" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="C266" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="267" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A267" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="B267" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="C267" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="268" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A268" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="B268" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="C268" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A269" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="B269" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C269" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A270" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="B270" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C270" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A271" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="B271" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C271" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A272" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="B272" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C272" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A273" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="B273" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="C273" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A274" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="B274" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="C274" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A275" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="B275" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="C275" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A276" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="B276" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="C276" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A277" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="B277" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="C277" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A278" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="B278" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C278" s="2" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A279" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="B279" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="C279" s="2" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A280" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="B280" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C280" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A281" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="B281" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="C281" s="2" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A282" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="B282" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C282" s="2" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A283" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="B283" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="C283" s="2" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A284" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="B284" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C284" s="2" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A285" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="B285" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="C285" s="2" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A286" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="B286" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C286" s="2" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A287" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="B287" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="C287" s="2" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A288" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="B288" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="C288" s="2">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="289" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A289" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="B289" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="C289" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="290" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A290" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="B290" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="C290" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="291" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A291" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="B291" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="C291" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="292" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A292" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="B292" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="C292" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="293" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A293" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="B293" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="C293" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="294" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A294" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="B294" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="C294" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="295" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A295" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="B295" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="C295" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="296" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A296" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="B296" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="C296" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="297" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A297" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="B297" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="C297" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="298" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A298" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="B298" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="C298" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="299" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A299" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="B299" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="C299" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="300" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A300" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="B300" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="C300" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="301" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A301" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="B301" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="C301" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="302" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A302" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="B302" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="C302" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="303" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A303" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="B303" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="C303" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="304" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A304" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="B304" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="C304" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A305" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="B305" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="C305" s="2">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A306" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="B306" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="C306" s="2">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A307" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="B307" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="C307" s="2">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A308" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="B308" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C308" s="2">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A309" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="B309" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C309" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A310" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="B310" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="C310" s="2">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A311" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="B311" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="C311" s="2">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A312" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="B312" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C312" s="2">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A313" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="B313" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C313" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="314" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A314" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B314" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="C314" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="315" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A315" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B315" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="C315" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="316" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A316" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B316" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="C316" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="317" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A317" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B317" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="C317" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="318" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A318" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B318" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="C318" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="319" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A319" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B319" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="C319" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="320" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A320" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B320" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="C320" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="321" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A321" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B321" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="C321" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="322" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A322" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B322" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="C322" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A323" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B323" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="C323" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="324" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A324" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B324" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="C324" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="325" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A325" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B325" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="C325" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="326" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A326" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B326" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="C326" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="327" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A327" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B327" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="C327" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="328" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A328" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B328" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="C328" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A329" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="B329" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C329" s="2" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="330" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A330" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="B330" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="C330" s="2">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="331" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A331" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="B331" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="C331" s="2">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="332" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A332" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="B332" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="C332" s="2">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="333" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A333" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="B333" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="C333" s="2">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A334" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="B334" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C334" s="2" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A335" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="B335" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C335" s="2" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="336" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A336" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="B336" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="C336" s="2" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="337" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A337" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="B337" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="C337" s="2" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="338" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A338" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="B338" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C338" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="339" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A339" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="B339" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="C339" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="340" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A340" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="B340" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="C340" s="2" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="341" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A341" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="B341" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="C341" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="342" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A342" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="B342" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C342" s="2" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="343" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A343" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="B343" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="C343" s="2">
-        <v>8086</v>
-      </c>
-    </row>
-    <row r="344" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A344" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="B344" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C344" s="2" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="345" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A345" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="B345" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="C345" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="346" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A346" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="B346" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C346" s="2" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="347" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A347" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="B347" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="C347" s="2" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="348" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A348" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="B348" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C348" s="2" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="349" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A349" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="B349" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="C349" s="2" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A350" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="B350" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="C350" s="2" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A351" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="B351" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="C351" s="2">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A352" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="B352" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="C352" s="2">
-        <v>386</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="B1:C403"/>
+  <autoFilter ref="B1:C153"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>